--- a/scripts/productos-digitales/guia-chocolateria/build/checklist-legal-licencias-y-cacao.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/checklist-legal-licencias-y-cacao.xlsx
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>SUPUESTO: la clasificacion urbanistica de un obrador no tiene fuente verificada. Va como PREGUNTA al ayuntamiento, nunca como afirmacion.  [Fuente: supuesto]</t>
+          <t>SUPUESTO: la clasificación urbanística de un obrador no tiene fuente verificada. Va como PREGUNTA al ayuntamiento, nunca como afirmación.  [Fuente: supuesto]</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Comprobar que ningun ayuntamiento puede exigirte licencia previa de actividad</t>
+          <t>Comprobar que ningún ayuntamiento puede exigirte licencia previa de actividad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>Para las actividades del Anexo de la Ley 12/2012 en establecimientos permanentes de hasta 750 m2 de superficie util de exposicion y venta al publico, NINGUNA administracion puede exigir licencia previa de instalacion, funcionamiento o actividad (`CHN-49`), y el Anexo incluye el grupo 644 completo, con el 644.5 de bombones y caramelos (`CHN-49b`). OJO: la chocolateria de TAZA queda fuera, porque el Anexo no contiene ningun grupo de la agrupacion 67 (`CHN-49c`). Y esta PROHIBIDO decir que tramite pide Madrid o Barcelona.  [Fuente: CHN-49 + CHN-49b]</t>
+          <t>Para las actividades del Anexo de la Ley 12/2012 en establecimientos permanentes de hasta 750 m² de superficie útil de exposición y venta al publico, NINGUNA administración puede exigir licencia previa de instalación, funcionamiento o actividad (`CHN-49`), y el Anexo incluye el grupo 644 completo, con el 644.5 de bombones y caramelos (`CHN-49b`). OJO: la chocolatería de TAZA queda fuera, porque el Anexo no contiene ningún grupo de la agrupación 67 (`CHN-49c`). Y esta PROHIBIDO decir que trámite pide Madrid o Barcelona.  [Fuente: CHN-49 + CHN-49b]</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Un obrador de chocolate NO genera aire AE4 (`CHN-46`) y el DB-HS 3 del CTE no regula la ventilacion de un local comercial (`CHN-45`): las reglas de chimenea que circulan son las de las viviendas. Lo que si aplica es el RITE, por la climatizacion.  [Fuente: CHN-45 + CHN-46]</t>
+          <t>Un obrador de chocolate NO genera aire AE4 (`CHN-46`) y el DB-HS 3 del CTE no regula la ventilación de un local comercial (`CHN-45`): las reglas de chimenea que circulan son las de las viviendas. Lo que si aplica es el RITE, por la climatización.  [Fuente: CHN-45 + CHN-46]</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Pedir al instalador la potencia frigorifica ofertada y las preguntas de la ficha</t>
+          <t>Pedir al instalador la potencia frigorífica ofertada y las preguntas de la ficha</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>El libro 1 NO calcula carga termica (D33): compara tu temperatura objetivo, la exterior de agosto de tu ciudad y la potencia que te OFREZCAN, y te da la ficha de preguntas.  [Fuente: supuesto]</t>
+          <t>El libro 1 NO calcula carga térmica (D33): compara tu temperatura objetivo, la exterior de agosto de tu ciudad y la potencia que te OFREZCAN, y te da la ficha de preguntas.  [Fuente: supuesto]</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>F2 · Sociedad, altas fiscales y proyecto tecnico</t>
+          <t>F2 · Sociedad, altas fiscales y proyecto técnico</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Constituir la sociedad o darse de alta como autonomo</t>
+          <t>Constituir la sociedad o darse de alta como autónomo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Importa para Verifactu: sociedad, 1-ene-2027; autonomo, 1-jul-2027 (`CHN-75`). NO es 2026.  [Fuente: supuesto]</t>
+          <t>Importa para Verifactu: sociedad, 1-ene-2027; autónomo, 1-jul-2027 (`CHN-75`). NO es 2026.  [Fuente: supuesto]</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Alta censal (modelo 036) con los DOS codigos CNAE</t>
+          <t>Alta censal (modelo 036) con los DOS códigos CNAE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>CNAE-2025: 10.82 «Fabricacion de cacao, chocolate y productos de confiteria» y 47.24 «Comercio al por menor de pan, productos de panaderia y confiteria» (`CHN-74`). Y al darte de alta HOY comunicas DOS codigos, no uno: el CNAE-2025 y ademas el CNAE-2009 mientras no entre en vigor la tarifa de primas adaptada (`CHN-74b`).  [Fuente: CHN-74 + CHN-74b]</t>
+          <t>CNAE-2025: 10.82 «Fabricación de cacao, chocolate y productos de confitería» y 47.24 «Comercio al por menor de pan, productos de panadería y confitería» (`CHN-74`). Y al darte de alta HOY comunicas DOS códigos, no uno: el CNAE-2025 y además el CNAE-2009 mientras no entre en vigor la tarifa de primas adaptada (`CHN-74b`).  [Fuente: CHN-74 + CHN-74b]</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Alta en el epigrafe 644.5 del IAE, con su nota literal delante</t>
+          <t>Alta en el epígrafe 644.5 del IAE, con su nota literal delante</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>El 644.5 «Comercio al por menor de bombones y caramelos» FACULTA para fabricar bombones en el propio establecimiento «siempre que su comercializacion se realice en las propias dependencias de venta» (`CHN-72`). Alta si, pago casi nunca: hay exencion por cifra de negocio (`CHN-73`). Y la Regla 4.a.1 dice que una cuota faculta EXCLUSIVAMENTE para su actividad (`CHN-94`): de ahi salen las cinco filas de canal.  [Fuente: CHN-72 + CHN-73 + CHN-94]</t>
+          <t>El 644.5 «Comercio al por menor de bombones y caramelos» FACULTA para fabricar bombones en el propio establecimiento «siempre que su comercialización se realice en las propias dependencias de venta» (`CHN-72`). Alta si, pago casi nunca: hay exención por cifra de negocio (`CHN-73`). Y la Regla 4.a.1 dice que una cuota faculta EXCLUSIVAMENTE para su actividad (`CHN-94`): de ahí salen las cinco filas de canal.  [Fuente: CHN-72 + CHN-73 + CHN-94]</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Alta en el regimen correspondiente de la Seguridad Social</t>
+          <t>Alta en el régimen correspondiente de la Seguridad Social</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Encargar el proyecto tecnico visado</t>
+          <t>Encargar el proyecto técnico visado</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Coste SUPUESTO: `CHN-50` esta en EXCLUIDOS. Es el documento del que cuelga todo lo demas.  [Fuente: supuesto]</t>
+          <t>Coste SUPUESTO: `CHN-50` esta en EXCLUIDOS. Es el documento del que cuelga todo lo demás.  [Fuente: supuesto]</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>F3 · Registro sanitario y comunicacion autonomica</t>
+          <t>F3 · Registro sanitario y comunicación autonómica</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Presentar la comunicacion o declaracion responsable al registro autonomico</t>
+          <t>Presentar la comunicación o declaración responsable al registro autonómico</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>El minorista esta EXCLUIDO del RGSEAA y se inscribe en el registro de su comunidad mediante comunicacion o declaracion responsable QUE NO HABILITA (`CHN-39`). Y el mismo tramite funciona distinto: en Madrid se presenta simultaneamente al inicio de la actividad y no habilita; en la Comunitat Valenciana es condicion unica y suficiente para iniciar y lleva tasa (`CHN-43`). PROHIBIDO escribir «necesitas el RGSEAA para abrir».  [Fuente: CHN-39 + CHN-43]</t>
+          <t>El minorista esta EXCLUIDO del RGSEAA y se inscribe en el registro de su comunidad mediante comunicación o declaración responsable QUE NO HABILITA (`CHN-39`). Y el mismo trámite funciona distinto: en Madrid se presenta simultaneamente al inicio de la actividad y no habilita; en la Comunitat Valenciana es condición única y suficiente para iniciar y lleva tasa (`CHN-43`). PROHIBIDO escribir «necesitas el RGSEAA para abrir».  [Fuente: CHN-39 + CHN-43]</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Resolver el arbol: tener obrador NO te saca de minorista</t>
+          <t>Resolver el árbol: tener obrador NO te saca de minorista</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Tener obrador NO te saca del regimen minorista (`CHN-40b`). La clave y las actividades del RGSEAA solo entran cuando SI toca (`CHN-40`).  [Fuente: CHN-40 + CHN-40b]</t>
+          <t>Tener obrador NO te saca del régimen minorista (`CHN-40b`). La clave y las actividades del RGSEAA solo entran cuando SI toca (`CHN-40`).  [Fuente: CHN-40 + CHN-40b]</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Resolver los TRES semaforos del art. 3 si suministras a otros minoristas</t>
+          <t>Resolver los TRES semáforos del art. 3 si suministras a otros minoristas</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>PUERTA DE ENTRADA: ¿suministras a otros minoristas de DISTINTA TITULARIDAD? Si la respuesta es no, el art. 3 no te aplica. Si es si, tres semaforos INDEPENDIENTES y ACUMULATIVOS: MARGINAL por la via a) hasta el 25 % del volumen anual O por la b) hasta 500 kg/semana -son dos entradas distintas-; LOCALIZADO, misma zona de salud o hasta 50 km en el caso interautonomico; RESTRINGIDO, que ninguno de tus clientes este inscrito en el RGSEAA. PROHIBIDO «los 500 kg incluyen el mostrador».  [Fuente: CHN-41]</t>
+          <t>PUERTA DE ENTRADA: ¿suministras a otros minoristas de DISTINTA TITULARIDAD? Si la respuesta es no, el art. 3 no te aplica. Si es si, tres semáforos INDEPENDIENTES y ACUMULATIVOS: MARGINAL por la vía a) hasta el 25 % del volumen anual O por la b) hasta 500 kg/semana -son dos entradas distintas-; LOCALIZADO, misma zona de salud o hasta 50 km en el caso interautonomico; RESTRINGIDO, que ninguno de tus clientes este inscrito en el RGSEAA. PROHIBIDO «los 500 kg incluyen el mostrador».  [Fuente: CHN-41]</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>La lista estatal del obrador en vivienda tiene CINCO letras y la quinta es ABIERTA: «otros alimentos que las autoridades competentes de las comunidades autonomas permitan en sus territorios» (`CHN-44`). Por defecto el chocolate no encaja en la letra b), pero eso es INTERPRETACION DECLARADA (`CHN-44-int`), no nivel A: compruebalo en tu comunidad. La letra b) valenciana anade «confiteria», NO «chocolate» (`CHN-44b`). PROHIBIDO «hacer bombones en casa para vender es ilegal en Espana». Y el tope de 100 kg/semana del art. 13.9 solo se activa si esta casilla esta en «si»: son TRES requisitos, no uno -volumen PROPORCIONAL AL TAMANO DE LAS INSTALACIONES, tope de 100 kg/semana y demostrable documentalmente- y el que de verdad limita es el primero (`PA-29c`, reutilizado de Pasteleria y verificado el 10-09-2026).  [Fuente: CHN-44 + CHN-44-int + CHN-44b]</t>
+          <t>La lista estatal del obrador en vivienda tiene CINCO letras y la quinta es ABIERTA: «otros alimentos que las autoridades competentes de las comunidades autónomas permitan en sus territorios» (`CHN-44`). Por defecto el chocolate no encaja en la letra b), pero eso es INTERPRETACION DECLARADA (`CHN-44-int`), no nivel A: compruebalo en tu comunidad. La letra b) valenciana añade «confitería», NO «chocolate» (`CHN-44b`). PROHIBIDO «hacer bombones en casa para vender es ilegal en Espana». Y el tope de 100 kg/semana del art. 13.9 solo se activa si esta casilla esta en «si»: son TRES requisitos, no uno -volumen PROPORCIONAL AL TAMAÑO DE LAS INSTALACIONES, tope de 100 kg/semana y demostrable documentalmente- y el que de verdad limita es el primero (`PA-29c`, reutilizado de Pastelería y verificado el 10-09-2026).  [Fuente: CHN-44 + CHN-44-int + CHN-44b]</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Contratar la obra y la adecuacion</t>
+          <t>Contratar la obra y la adecuación</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Coste SUPUESTO. Sin humos, la obra de un obrador de chocolate es mas barata que la de una pasteleria.  [Fuente: supuesto]</t>
+          <t>Coste SUPUESTO. Sin humos, la obra de un obrador de chocolate es mas barata que la de una pastelería.  [Fuente: supuesto]</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Contratar la climatizacion con deshumidificacion</t>
+          <t>Contratar la climatización con deshumidificación</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Solo si FABRICAS, IMPORTAS o haces ADQUISICION INTRACOMUNITARIA de envases no reutilizables con plastico. La exencion del art. 75.f) (5 kg/mes) cubre solo la importacion y la adquisicion intracomunitaria, y solo los envases del art. 68.1.a): NO la fabricacion, NI los semielaborados, NI los cierres (`CHN-62b`).  [Fuente: CHN-62 + CHN-62b]</t>
+          <t>Solo si FABRICAS, IMPORTAS o haces ADQUISICION INTRACOMUNITARIA de envases no reutilizables con plastico. La exención del art. 75.f) (5 kg/mes) cubre solo la importación y la adquisición intracomunitaria, y solo los envases del art. 68.1.a): NO la fabricación, NI los semielaborados, NI los cierres (`CHN-62b`).  [Fuente: CHN-62 + CHN-62b]</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Si hay freidora de gas en la variante de taza, programar la inspeccion</t>
+          <t>Si hay freidora de gas en la variante de taza, programar la inspección</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>Inspeccion periodica obligatoria de la instalacion receptora CADA CINCO ANOS, que en instalaciones de hasta 70 kW incluye los aparatos y comprueba la ventilacion y el volumen minimo del local (`CHN-48`).  [Fuente: CHN-48]</t>
+          <t>Inspección periódica obligatoria de la instalación receptora CADA CINCO AÑOS, que en instalaciones de hasta 70 kW incluye los aparatos y comprueba la ventilación y el volumen mínimo del local (`CHN-48`).  [Fuente: CHN-48]</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>F5 · APPCC, alergenos y formacion</t>
+          <t>F5 · APPCC, alérgenos y formación</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>El procedimiento permanente basado en el APPCC puede aplicarse de manera SIMPLIFICADA conforme a la Comunicacion 2020/C 199/01, pero debe contar con una persona responsable de su aplicacion (`CHN-32`). En el APPCC va la vida util que TU declaras (`CHN-30`).  [Fuente: CHN-32]</t>
+          <t>El procedimiento permanente basado en el APPCC puede aplicarse de manera SIMPLIFICADA conforme a la Comunicación 2020/C 199/01, pero debe contar con una persona responsable de su aplicación (`CHN-32`). En el APPCC va la vida útil que TU declaras (`CHN-30`).  [Fuente: CHN-32]</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Montar el registro de formacion del personal</t>
+          <t>Montar el registro de formación del personal</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>EL CARNET DE MANIPULADOR NO EXISTE. La obligacion viva es del empresario: garantizar la formacion de cada persona de acuerdo con su actividad laboral y PODER ACREDITARLA (`CHN-69`). PROHIBIDO escribir «hay que sacarse el carnet de manipulador».  [Fuente: CHN-69]</t>
+          <t>EL CARNET DE MANIPULADOR NO EXISTE. La obligación viva es del empresario: garantizar la formación de cada persona de acuerdo con su actividad laboral y PODER ACREDITARLA (`CHN-69`). PROHIBIDO escribir «hay que sacarse el carnet de manipulador».  [Fuente: CHN-69]</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Montar la declaracion de los OCHO alergenos y el protocolo de limpieza</t>
+          <t>Montar la declaración de los OCHO alérgenos y el protocolo de limpieza</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>OCHO, no cinco (`CHN-34b`). El equipo usado con un alergeno no se reutiliza para otro alimento sin limpiarlo (`CHN-33`). En producto sin envasar los alergenos pueden ir en cartel, pero la fecha no (`CHN-89`).  [Fuente: CHN-34b + CHN-33 + CHN-89]</t>
+          <t>OCHO, no cinco (`CHN-34b`). El equipo usado con un alérgeno no se reutiliza para otro alimento sin limpiarlo (`CHN-33`). En producto sin envasar los alérgenos pueden ir en cartel, pero la fecha no (`CHN-89`).  [Fuente: CHN-34b + CHN-33 + CHN-89]</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>NO ES EL MISMO REGIMEN (D47). Con etiqueta te obliga lo que tu has escrito en ella (art. 4.2 del RD 1021/2022) mas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) y el lote, que viene del RD 1808/1991 y NO de ese reglamento (`CHN-36`). A granel, la referencia es TU sistema de autocontrol.  [Fuente: CHN-30 + CHN-35 + CHN-36 + CHN-87]</t>
+          <t>NO ES EL MISMO RÉGIMEN (D47). Con etiqueta te obliga lo que tu has escrito en ella (art. 4.2 del RD 1021/2022) mas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) y el lote, que viene del RD 1808/1991 y NO de ese reglamento (`CHN-36`). A granel, la referencia es TU sistema de autocontrol.  [Fuente: CHN-30 + CHN-35 + CHN-36 + CHN-87]</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Decidir si necesitas analitica de cadmio y con que frecuencia</t>
+          <t>Decidir si necesitas analítica de cadmio y con que frecuencia</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>LO QUE ES CHOCOLATE PARA LA DENOMINACION NO LO ES PARA LOS CONTAMINANTES: la nota (14) del Anexo I del Rgto. 2023/915 remite SOLO a los puntos 2, 3 y 4 de la parte A del Anexo I de la Directiva 2000/36/CE -cacao en polvo, chocolate y chocolate con leche- (`CHN-16b`). El BOMBON NO TIENE LIMITE PROPIO DE CADMIO: se le aplica la regla de alimentos compuestos del art. 3 (`CHN-84`). PROHIBIDO «tu bombon tiene un limite de cadmio de X».  [Fuente: CHN-16 + CHN-16b + CHN-84]</t>
+          <t>LO QUE ES CHOCOLATE PARA LA DENOMINACION NO LO ES PARA LOS CONTAMINANTES: la nota (14) del Anexo I del Rgto. 2023/915 remite SOLO a los puntos 2, 3 y 4 de la parte A del Anexo I de la Directiva 2000/36/CE -cacao en polvo, chocolate y chocolate con leche- (`CHN-16b`). El BOMBÓN NO TIENE LIMITE PROPIO DE CADMIO: se le aplica la regla de alimentos compuestos del art. 3 (`CHN-84`). PROHIBIDO «tu bombón tiene un limite de cadmio de X».  [Fuente: CHN-16 + CHN-16b + CHN-84]</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>El Anexo I incluye la partida 1806 «Chocolate y demas preparaciones alimenticias que contengan cacao», y el reglamento cubre tambien la EXPORTACION (`CHN-20`, `CHN-60`). Fecha general: 30 de diciembre de 2026 (`CHN-21`). El aplazamiento a 30-06-2027 del art. 38.3 es SOLO para «operadores» persona fisica, microempresa o pequena empresa establecidos a 31-12-2024, y el art. 2.15 excluye de esa palabra a los operadores posteriores (`CHN-22`, `CHN-23`). VERIFICADO A 12-09-2026: comprueba el estado del EUDR antes de comprar cacao.  [Fuente: CHN-20 + CHN-21 + CHN-22 + CHN-23 + CHN-24 + CHN-25]</t>
+          <t>El Anexo I incluye la partida 1806 «Chocolate y demás preparaciones alimenticias que contengan cacao», y el reglamento cubre también la EXPORTACION (`CHN-20`, `CHN-60`). Fecha general: 30 de diciembre de 2026 (`CHN-21`). El aplazamiento a 30-06-2027 del art. 38.3 es SOLO para «operadores» persona física, microempresa o pequeña empresa establecidos a 31-12-2024, y el art. 2.15 excluye de esa palabra a los operadores posteriores (`CHN-22`, `CHN-23`). VERIFICADO A 12-09-2026: comprueba el estado del EUDR antes de comprar cacao.  [Fuente: CHN-20 + CHN-21 + CHN-22 + CHN-23 + CHN-24 + CHN-25]</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Comprobar que tu comunicacion sanitaria esta presentada antes de vender</t>
+          <t>Comprobar que tu comunicación sanitaria esta presentada antes de vender</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>NO EXISTE convenio estatal del chocolate (`CHN-66`). La tabla que trae el producto es la de Madrid y va MARCADA COMO EJEMPLO. Busca el tuyo por AMBITO FUNCIONAL, no por el nombre que te suene: la denominacion oficial del de Madrid es «CONFITERIAS PASTELERIAS Y REPOSTERIA (COMERCIO E INDUSTRIA)» y quien busque «bollerias» no lo encuentra (`CHN-65c`). Cuatro convenios de sector nombran chocolates o bombones (`CHN-93`).  [Fuente: CHN-65 + CHN-65c + CHN-66 + CHN-93]</t>
+          <t>NO EXISTE convenio estatal del chocolate (`CHN-66`). La tabla que trae el producto es la de Madrid y va MARCADA COMO EJEMPLO. Busca el tuyo por ÁMBITO FUNCIONAL, no por el nombre que te suene: la denominación oficial del de Madrid es «CONFITERÍAS PASTELERÍAS Y REPOSTERÍA (COMERCIO E INDUSTRIA)» y quien busque «bollerias» no lo encuentra (`CHN-65c`). Cuatro convenios de sector nombran chocolates o bombones (`CHN-93`).  [Fuente: CHN-65 + CHN-65c + CHN-66 + CHN-93]</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Una bomboneria NO esta en la lista del art. 5.1 de la Ley 1/2004 -que nombra «pasteleria y reposteria, pan, platos preparados, prensa, combustibles y carburantes, floristerias y plantas»-: le viene por el art. 5.2, establecimientos de venta de reducida dimension de menos de 300 m2 (`CHN-77`). PROHIBIDO decir que le viene por el 5.1, y prohibido «hay que pedir permiso para abrir en domingo».  [Fuente: CHN-77]</t>
+          <t>Una bombonería NO esta en la lista del art. 5.1 de la Ley 1/2004 -que nombra «pastelería y repostería, pan, platos preparados, prensa, combustibles y carburantes, floristerias y plantas»-: le viene por el art. 5.2, establecimientos de venta de reducida dimensión de menos de 300 m² (`CHN-77`). PROHIBIDO decir que le viene por el 5.1, y prohibido «hay que pedir permiso para abrir en domingo».  [Fuente: CHN-77]</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Decidir si publicas precios anteriores, y con la regla de los 30 dias delante</t>
+          <t>Decidir si publicas precios anteriores, y con la regla de los 30 días delante</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>Subir en noviembre para «rebajar» en diciembre NO cumple la regla de los 30 dias del art. 20 de la LEY 7/1996 en la redaccion del RDL 24/2021 (`CHN-76`) - que NO es el art. 20 del TRLGDCU. Por eso este producto sale SIN precio tachado.  [Fuente: CHN-76]</t>
+          <t>Subir en noviembre para «rebajar» en diciembre NO cumple la regla de los 30 días del art. 20 de la LEY 7/1996 en la redacción del RDL 24/2021 (`CHN-76`) - que NO es el art. 20 del TRLGDCU. Por eso este producto sale SIN precio tachado.  [Fuente: CHN-76]</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>El art. 6.6 de la Ley 1/2025 EXCLUYE a las microempresas de las obligaciones de TODOS los apartados anteriores del art. 6 -plan, convenios de donacion, jerarquia- (`CHN-64`). Lo que sigue en pie no es una obligacion tuya: es que cualquier clausula contractual que prohiba donar es nula de pleno derecho. PERO la exclusion NO alcanza al ART. 8 (`CHN-92`), que obliga a las empresas de hosteleria y otros proveedores de servicios alimentarios a facilitar que el consumidor se lleve lo que no ha consumido. PROHIBIDAS las dos frases: «te siguen obligando el 6.2 y el 6.5» y «no te obliga nada de la ley de desperdicio».  [Fuente: CHN-64 + CHN-92]</t>
+          <t>El art. 6.6 de la Ley 1/2025 EXCLUYE a las microempresas de las obligaciones de TODOS los apartados anteriores del art. 6 -plan, convenios de donación, jerarquia- (`CHN-64`). Lo que sigue en pie no es una obligación tuya: es que cualquier clausula contractual que prohíba donar es nula de pleno derecho. PERO la exclusión NO alcanza al ART. 8 (`CHN-92`), que obliga a las empresas de hostelería y otros proveedores de servicios alimentarios a facilitar que el consumidor se lleve lo que no ha consumido. PROHIBIDAS las dos frases: «te siguen obligando el 6.2 y el 6.5» y «no te obliga nada de la ley de desperdicio».  [Fuente: CHN-64 + CHN-92]</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
     <row r="70" ht="40" customHeight="1">
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>¿Vas a inscribirte como artesano alimentario? (comunidad autonoma + enlace)</t>
+          <t>¿Vas a inscribirte como artesano alimentario? (comunidad autónoma + enlace)</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>Cataluna tiene articulado con el chocolate dentro: su repertorio de artesania alimentaria incluye «Pasteleria: elaboracion de productos de confiteria, pasteleria, bolleria y reposteria, INCLUIDOS TURRONES Y CHOCOLATES» (`CHN-52`). Es una ACREDITACION VOLUNTARIA y queda PROHIBIDO escribir que sin ella no puedes llamarte artesanal. Y queda PROHIBIDO usar ese decreto como prueba de que es «reposteria» para el RD 1021/2022: es otro registro, otra competencia y otro fin. «Chocolate artesano» no tiene definicion estatal: «artesano», «artesanal» y «casero» tienen CERO ocurrencias en el RD 1055/2003 y en el RD 496/2010 (`CHN-53`). En el resto de comunidades, enlace a su registro.</t>
+          <t>Cataluña tiene articulado con el chocolate dentro: su repertorio de artesanía alimentaria incluye «Pastelería: elaboración de productos de confitería, pastelería, bollería y repostería, INCLUIDOS TURRONES Y CHOCOLATES» (`CHN-52`). Es una ACREDITACION VOLUNTARIA y queda PROHIBIDO escribir que sin ella no puedes llamarte artesanal. Y queda PROHIBIDO usar ese decreto como prueba de que es «repostería» para el RD 1021/2022: es otro registro, otra competencia y otro fin. «Chocolate artesano» no tiene definición estatal: «artesano», «artesanal» y «casero» tienen CERO ocurrencias en el RD 1055/2003 y en el RD 496/2010 (`CHN-53`). En el resto de comunidades, enlace a su registro.</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="F74" s="25" t="inlineStr">
         <is>
-          <t>Mi epigrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender ademas por este canal: Mostrador. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epigrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
+          <t>Mi epígrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender además por este canal: Mostrador. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epígrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Online con envio refrigerado</t>
+          <t>Online con envío refrigerado</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F75" s="25" t="inlineStr">
         <is>
-          <t>Mi epigrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender ademas por este canal: Online con envio refrigerado. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epigrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
+          <t>Mi epígrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender además por este canal: Online con envío refrigerado. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epígrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>B2B a hosteleria</t>
+          <t>B2B a hostelería</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="F76" s="25" t="inlineStr">
         <is>
-          <t>Mi epigrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender ademas por este canal: B2B a hosteleria. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epigrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
+          <t>Mi epígrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender además por este canal: B2B a hostelería. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epígrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="F77" s="25" t="inlineStr">
         <is>
-          <t>Mi epigrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender ademas por este canal: Regalo corporativo. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epigrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
+          <t>Mi epígrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender además por este canal: Regalo corporativo. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epígrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F78" s="25" t="inlineStr">
         <is>
-          <t>Mi epigrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender ademas por este canal: Talleres y catas. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epigrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
+          <t>Mi epígrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender además por este canal: Talleres y catas. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epígrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="B11" s="38" t="inlineStr">
         <is>
-          <t>No lo sé</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Depende de si encaja en «cacao en polvo» o es una preparación con otros ingredientes. Míralo referencia a referencia con la denominación legal que le hayas dado en el libro 4.</t>
+          <t>Los puntos 8 y 9 de la Directiva -el chocolate a la taza- quedan FUERA de la nota (14): alimento compuesto, art. 3 del Rgto. 2023/915. Distinto es el cacao en polvo vendido como tal, que sí tiene límite propio: míralo referencia a referencia con la denominación legal que le hayas dado en el libro 4.</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Hace la PRIMERA comercializacion en el mercado de la Union, o exporta. Si es tu caso -por ejemplo, importas grano para bean-to-bar-, te toca diligencia debida COMPLETA antes de introducir en el mercado, declaracion presentada previamente, asuncion de responsabilidad y registro de las declaraciones durante cinco anos (`CHN-25`). A ESTE proveedor SI hay que pedirle el numero de referencia de su DDS.</t>
+          <t>Hace la PRIMERA comercialización en el mercado de la Unión, o exporta. Si es tu caso -por ejemplo, importas grano para bean-to-bar-, te toca diligencia debida COMPLETA antes de introducir en el mercado, declaración presentada previamente, asunción de responsabilidad y registro de las declaraciones durante cinco años (`CHN-25`). A ESTE proveedor SI hay que pedirle el número de referencia de su DDS.</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Introduce en el mercado productos elaborados con otros productos YA amparados por una declaracion de diligencia debida (`CHN-23`, art. 2.15 ter). Es lo que normalmente sera una chocolateria que compra cobertura ya comercializada en la UE. A este NO se le pide el numero de DDS por el art. 5.3.a).</t>
+          <t>Introduce en el mercado productos elaborados con otros productos YA amparados por una declaración de diligencia debida (`CHN-23`, art. 2.15 ter). Es lo que normalmente será una chocolatería que compra cobertura ya comercializada en la UE. A este NO se le pide el número de DDS por el art. 5.3.a).</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Ni introduce ni exporta: comercia dentro. Tampoco se le pide el numero de DDS.</t>
+          <t>Ni introduce ni exporta: comercia dentro. Tampoco se le pide el número de DDS.</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
     <row r="29" ht="92" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>REDACCION OBLIGATORIA, y el paso es INFERENCIA DECLARADA, no nivel A: «si tu cobertura llega ya comercializada en la UE y amparada por una declaracion de diligencia debida, eres operador posterior (art. 2.15 ter) y el aplazamiento del art. 38.3 -que es para operadores- no te alcanza: tu fecha es el 30 de diciembre de 2026. Si tu cobertura NO esta amparada (compra anterior al EUDR, proveedor que no lo acredita), la calificacion deja de ser automatica y hay que revisarla». Estan PROHIBIDAS «siempre eres operador posterior» y «tu fecha es el 30-12-2026 pase lo que pase». Y la exclusion de los operadores posteriores del punto 15 se PARAFRASEA, no se entrecomilla: consta en la nota de `CHN-22`, no entre las 81 citas del gate de literalidad. Verificado a 12-09-2026: comprueba el estado del EUDR antes de comprar cacao.</t>
+          <t>REDACCION OBLIGATORIA, y el paso es INFERENCIA DECLARADA, no nivel A: «si tu cobertura llega ya comercializada en la UE y amparada por una declaración de diligencia debida, eres operador posterior (art. 2.15 ter) y el aplazamiento del art. 38.3 -que es para operadores- no te alcanza: tu fecha es el 30 de diciembre de 2026. Si tu cobertura NO esta amparada (compra anterior al EUDR, proveedor que no lo acredita), la calificación deja de ser automática y hay que revisarla». Están PROHIBIDAS «siempre eres operador posterior» y «tu fecha es el 30-12-2026 pase lo que pase». Y la exclusión de los operadores posteriores del punto 15 se PARAFRASEA, no se entrecomilla: consta en la nota de `CHN-22`, no entre las 81 citas del gate de literalidad. Verificado a 12-09-2026: comprueba el estado del EUDR antes de comprar cacao.</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="E7" s="43" t="inlineStr">
         <is>
-          <t>Higiene, alérgenos y trazabilidad aplicados a el obrador</t>
+          <t>Higiene, alérgenos y trazabilidad aplicados al obrador</t>
         </is>
       </c>
       <c r="F7" s="14" t="n">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Manana (07:00-15:00)</t>
+          <t>Mañana (07:00-15:00)</t>
         </is>
       </c>
       <c r="E8" s="43" t="inlineStr">
         <is>
-          <t>Higiene, alérgenos y trazabilidad aplicados a el obrador</t>
+          <t>Higiene, alérgenos y trazabilidad aplicados al obrador</t>
         </is>
       </c>
       <c r="F8" s="14" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Proyecto tecnico visado</t>
+          <t>Proyecto técnico visado</t>
         </is>
       </c>
       <c r="C11" s="37" t="n">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Declaracion responsable de actividad (no licencia previa)</t>
+          <t>Declaración responsable de actividad (no licencia previa)</t>
         </is>
       </c>
       <c r="C12" s="37" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Obra y adecuacion del local</t>
+          <t>Obra y adecuación del local</t>
         </is>
       </c>
       <c r="C13" s="37" t="n">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Climatizacion y deshumidificacion</t>
+          <t>Climatización y deshumidificación</t>
         </is>
       </c>
       <c r="C15" s="37" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Comunicacion al registro sanitario autonomico</t>
+          <t>Comunicación al registro sanitario autonómico</t>
         </is>
       </c>
       <c r="C17" s="37" t="n">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Plan de APPCC, alergenos y registro de formacion</t>
+          <t>Plan de APPCC, alérgenos y registro de formación</t>
         </is>
       </c>
       <c r="C18" s="37" t="n">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Contratacion del equipo y altas en Seguridad Social</t>
+          <t>Contratación del equipo y altas en Seguridad Social</t>
         </is>
       </c>
       <c r="C19" s="37" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>San Valentin</t>
+          <t>San Valentín</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Dia del Padre</t>
+          <t>Día del Padre</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>COMUNIONES (pico) y Dia de la Madre</t>
+          <t>COMUNIONES (pico) y Día de la Madre</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>COMUNIONES (ultimas)</t>
+          <t>COMUNIONES (últimas)</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">

--- a/scripts/productos-digitales/guia-chocolateria/build/checklist-legal-licencias-y-cacao.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/checklist-legal-licencias-y-cacao.xlsx
@@ -2381,7 +2381,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>La lista estatal del obrador en vivienda tiene CINCO letras y la quinta es ABIERTA: «otros alimentos que las autoridades competentes de las comunidades autónomas permitan en sus territorios» (`CHN-44`). Por defecto el chocolate no encaja en la letra b), pero eso es INTERPRETACION DECLARADA (`CHN-44-int`), no nivel A: compruebalo en tu comunidad. La letra b) valenciana añade «confitería», NO «chocolate» (`CHN-44b`). PROHIBIDO «hacer bombones en casa para vender es ilegal en Espana». Y el tope de 100 kg/semana del art. 13.9 solo se activa si esta casilla esta en «si»: son TRES requisitos, no uno -volumen PROPORCIONAL AL TAMAÑO DE LAS INSTALACIONES, tope de 100 kg/semana y demostrable documentalmente- y el que de verdad limita es el primero (`PA-29c`, reutilizado de Pastelería y verificado el 10-09-2026).  [Fuente: CHN-44 + CHN-44-int + CHN-44b]</t>
+          <t>La lista estatal del obrador en vivienda tiene CINCO letras y la quinta es ABIERTA: «otros alimentos que las autoridades competentes de las comunidades autónomas permitan en sus territorios» (`CHN-44`). Por defecto el chocolate no encaja en la letra b), pero eso es INTERPRETACION DECLARADA (`CHN-44-int`), no nivel A: compruebalo en tu comunidad. La letra b) valenciana añade «confitería», NO «chocolate» (`CHN-44b`). PROHIBIDO «hacer bombones en casa para vender es ilegal en España». Y el tope de 100 kg/semana del art. 13.9 solo se activa si esta casilla esta en «si»: son TRES requisitos, no uno -volumen PROPORCIONAL AL TAMAÑO DE LAS INSTALACIONES, tope de 100 kg/semana y demostrable documentalmente- y el que de verdad limita es el primero (`PA-29c`, reutilizado de Pastelería y verificado el 10-09-2026).  [Fuente: CHN-44 + CHN-44-int + CHN-44b]</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Hace la PRIMERA comercialización en el mercado de la Unión, o exporta. Si es tu caso -por ejemplo, importas grano para bean-to-bar-, te toca diligencia debida COMPLETA antes de introducir en el mercado, declaración presentada previamente, asunción de responsabilidad y registro de las declaraciones durante cinco años (`CHN-25`). A ESTE proveedor SI hay que pedirle el número de referencia de su DDS.</t>
+          <t>Hace la PRIMERA comercialización en el mercado de la Unión, o exporta. Si es tu caso -por ejemplo, importas grano para bean-to-bar-, te toca diligencia debida COMPLETA antes de introducir en el mercado, declaración presentada previamente, asunción de responsabilidad y registro de las declaraciones durante cinco años (CHN-25). A ESTE proveedor SI hay que pedirle el número de referencia de su DDS.</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Introduce en el mercado productos elaborados con otros productos YA amparados por una declaración de diligencia debida (`CHN-23`, art. 2.15 ter). Es lo que normalmente será una chocolatería que compra cobertura ya comercializada en la UE. A este NO se le pide el número de DDS por el art. 5.3.a).</t>
+          <t>Introduce en el mercado productos elaborados con otros productos YA amparados por una declaración de diligencia debida (CHN-23, art. 2.15 ter). Es lo que normalmente será una chocolatería que compra cobertura ya comercializada en la UE. A este NO se le pide el número de DDS por el art. 5.3.a).</t>
         </is>
       </c>
     </row>
